--- a/braph2individualconnectome/pipelines/group_data/test/atlas/aal94_atlas.xlsx
+++ b/braph2individualconnectome/pipelines/group_data/test/atlas/aal94_atlas.xlsx
@@ -738,7 +738,8 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -909,7 +910,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>18</v>
       </c>
@@ -929,7 +930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>20</v>
       </c>
@@ -949,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>22</v>
       </c>
@@ -969,7 +970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>24</v>
       </c>
@@ -1009,7 +1010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>28</v>
       </c>
@@ -1189,7 +1190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>46</v>
       </c>
@@ -1209,7 +1210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>48</v>
       </c>
@@ -1469,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
         <v>74</v>
       </c>
@@ -1489,7 +1490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>76</v>
       </c>
@@ -1509,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
         <v>78</v>
       </c>
@@ -1529,7 +1530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
         <v>80</v>
       </c>
@@ -1709,7 +1710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
         <v>98</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>100</v>
       </c>
@@ -2509,7 +2510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
         <v>177</v>
       </c>
@@ -2529,7 +2530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
         <v>179</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
         <v>185</v>
       </c>
@@ -2609,7 +2610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
         <v>187</v>
       </c>
